--- a/resources/templates/sq_gap_forms/05_금형_점검체크시트_L1100-20.xlsx
+++ b/resources/templates/sq_gap_forms/05_금형_점검체크시트_L1100-20.xlsx
@@ -64,7 +64,7 @@
         <sz val="8"/>
         <rFont val="맑은 고딕"/>
       </rPr>
-      <t>: L1100-20(</t>
+      <t>: L1100-25(</t>
     </r>
     <r>
       <rPr>
@@ -773,7 +773,7 @@
         <sz val="8"/>
         <rFont val="맑은 고딕"/>
       </rPr>
-      <t>: L1100-20(</t>
+      <t>: L1100-25(</t>
     </r>
     <r>
       <rPr>
@@ -5226,7 +5226,7 @@
     <mergeCell ref="H3:J3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
